--- a/escape_rooms_tracker_mejorado.xlsx
+++ b/escape_rooms_tracker_mejorado.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Isaac\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\iborras\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{417E6A7B-F4EF-443A-B82A-EEA14937354F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{38695096-D7A6-4480-A1A1-0AF4A0BE9585}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Pendientes" sheetId="1" r:id="rId1"/>
@@ -27,15 +27,12 @@
         <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
     </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="306" uniqueCount="215">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="315" uniqueCount="220">
   <si>
     <t>Nombre del Escape</t>
   </si>
@@ -690,6 +687,26 @@
 En cuanto a jugadores, para nosotros 4 personas fue el número ideal. Todos participamos activamente en las pruebas y nadie se quedó mirando. Con grupos más grandes quizá podría quedarse algo corto.
 Entre la introducción, la partida y la charla final con el GM estuvimos cerca de una hora y media disfrutando de la experiencia.
 Un escape room muy recomendable para familias y para cualquier fan de **Los Goonies**. ¡Los Goonies nunca dicen muerto!</t>
+  </si>
+  <si>
+    <t>Visitamos Nightshift en Sabadell y salimos encantados. Fuimos 4 adultos, dos de ellos con más de 50 escapes a sus espaldas, y aun así ha conseguido entrar directamente en nuestro TOP de salas.
+Una experiencia muy inmersiva, con momentos de tensión, situaciones de soledad, pruebas de valentía y alguna sorpresa que no habíamos visto en ningún otro escape room. Los juegos de luces, la música, los efectos y la ambientación están perfectamente medidos para mantener la tensión durante toda la partida. Esos pasillos largos y oscuros, las puertas cerradas... o quizá no tanto... hacen que nunca te relajes del todo.
+Las 2 horas de juego se nos pasaron volando.
+Mención especial para nuestra GM, Laura, que estuvo fantástica de principio a fin. Muy amable, totalmente implicada en la experiencia y con una charla final genial. Toda una artista.
+Además, al estar ubicado en un polígono industrial, aparcar es muy fácil.
+Si os gustan las experiencias inmersivas y las emociones fuertes, Nightshift es una apuesta segura.</t>
+  </si>
+  <si>
+    <t>Nightshift</t>
+  </si>
+  <si>
+    <t>Crupont Legacy</t>
+  </si>
+  <si>
+    <t>8.62</t>
+  </si>
+  <si>
+    <t>https://www.crupontlegacy.com/</t>
   </si>
 </sst>
 </file>
@@ -838,38 +855,38 @@
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs count="24">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
@@ -886,10 +903,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<x18tc:personList xmlns:x18tc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1094,20 +1107,20 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:L39"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="12.7109375" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="39.88671875" customWidth="1"/>
-    <col min="2" max="2" width="14" customWidth="1"/>
-    <col min="3" max="3" width="7.21875" customWidth="1"/>
-    <col min="4" max="4" width="8.6640625" customWidth="1"/>
-    <col min="6" max="6" width="6.109375" customWidth="1"/>
-    <col min="7" max="7" width="7" customWidth="1"/>
-    <col min="8" max="8" width="8.77734375" customWidth="1"/>
-    <col min="9" max="9" width="61.77734375" customWidth="1"/>
-    <col min="10" max="10" width="13.88671875" customWidth="1"/>
-    <col min="11" max="11" width="11.33203125" customWidth="1"/>
-    <col min="12" max="12" width="370.44140625" customWidth="1"/>
-    <col min="13" max="13" width="145.21875" customWidth="1"/>
+    <col min="1" max="1" width="53.85546875" customWidth="1"/>
+    <col min="2" max="2" width="24" customWidth="1"/>
+    <col min="3" max="3" width="7.28515625" customWidth="1"/>
+    <col min="4" max="4" width="8.7109375" customWidth="1"/>
+    <col min="6" max="6" width="6.140625" customWidth="1"/>
+    <col min="7" max="7" width="17.5703125" customWidth="1"/>
+    <col min="8" max="8" width="8.7109375" customWidth="1"/>
+    <col min="9" max="9" width="61.7109375" customWidth="1"/>
+    <col min="10" max="10" width="13.85546875" customWidth="1"/>
+    <col min="11" max="11" width="11.28515625" customWidth="1"/>
+    <col min="12" max="12" width="370.42578125" customWidth="1"/>
+    <col min="13" max="13" width="145.28515625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="15.75" customHeight="1">
@@ -1880,7 +1893,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="22" spans="1:12" ht="13.2">
+    <row r="22" spans="1:12" ht="12.75">
       <c r="A22" s="2" t="s">
         <v>136</v>
       </c>
@@ -1912,31 +1925,31 @@
         <v>140</v>
       </c>
     </row>
-    <row r="35" spans="1:5" ht="13.2">
+    <row r="35" spans="1:5" ht="12.75">
       <c r="A35" s="16"/>
       <c r="B35" s="16"/>
       <c r="C35" s="16"/>
       <c r="D35" s="16"/>
       <c r="E35" s="16"/>
     </row>
-    <row r="36" spans="1:5" ht="13.2">
+    <row r="36" spans="1:5" ht="12.75">
       <c r="A36" s="19"/>
       <c r="B36" s="15"/>
       <c r="C36" s="16"/>
       <c r="D36" s="16"/>
       <c r="E36" s="16"/>
     </row>
-    <row r="37" spans="1:5" ht="13.2">
+    <row r="37" spans="1:5" ht="12.75">
       <c r="A37" s="19"/>
       <c r="B37" s="15"/>
       <c r="C37" s="16"/>
       <c r="D37" s="16"/>
     </row>
-    <row r="38" spans="1:5" ht="13.2">
+    <row r="38" spans="1:5" ht="12.75">
       <c r="A38" s="19"/>
       <c r="D38" s="16"/>
     </row>
-    <row r="39" spans="1:5" ht="13.2">
+    <row r="39" spans="1:5" ht="12.75">
       <c r="A39" s="19"/>
       <c r="D39" s="16"/>
     </row>
@@ -1973,22 +1986,22 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:P15"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1"/>
+  <dimension ref="A1:P16"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="12.7109375" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="20.88671875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="25.44140625" customWidth="1"/>
-    <col min="4" max="4" width="15.77734375" customWidth="1"/>
-    <col min="5" max="5" width="16.21875" customWidth="1"/>
-    <col min="8" max="8" width="15.21875" customWidth="1"/>
-    <col min="9" max="9" width="36.109375" customWidth="1"/>
-    <col min="10" max="10" width="14.21875" customWidth="1"/>
-    <col min="11" max="11" width="14.109375" customWidth="1"/>
-    <col min="12" max="15" width="11.77734375" customWidth="1"/>
+    <col min="1" max="1" width="22.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="33.7109375" customWidth="1"/>
+    <col min="4" max="4" width="15.7109375" customWidth="1"/>
+    <col min="5" max="5" width="16.28515625" customWidth="1"/>
+    <col min="8" max="8" width="15.28515625" customWidth="1"/>
+    <col min="9" max="9" width="69.85546875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="20.140625" customWidth="1"/>
+    <col min="11" max="11" width="14.140625" customWidth="1"/>
+    <col min="12" max="15" width="11.7109375" customWidth="1"/>
     <col min="16" max="16" width="166" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" ht="14.4">
+    <row r="1" spans="1:16" ht="15">
       <c r="A1" s="20" t="s">
         <v>0</v>
       </c>
@@ -2054,7 +2067,7 @@
       <c r="E2" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="F2" s="3">
+      <c r="F2" s="1">
         <v>70</v>
       </c>
       <c r="G2" s="1" t="s">
@@ -2066,12 +2079,12 @@
       <c r="I2" s="6" t="s">
         <v>152</v>
       </c>
-      <c r="J2" s="21">
-        <f t="shared" ref="J2:J13" si="0">AVERAGE(L2:O2)</f>
+      <c r="J2" s="2">
+        <f t="shared" ref="J2:J16" si="0">AVERAGE(L2:O2)</f>
         <v>9.375</v>
       </c>
-      <c r="K2" s="21">
-        <f t="shared" ref="K2:K15" si="1">RANK(J2, $J$2:$J$22)</f>
+      <c r="K2" s="2">
+        <f t="shared" ref="K2:K16" si="1">RANK(J2, $J$2:$J$22)</f>
         <v>2</v>
       </c>
       <c r="L2" s="2">
@@ -2106,7 +2119,7 @@
       <c r="E3" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="F3" s="3">
+      <c r="F3" s="1">
         <v>60</v>
       </c>
       <c r="G3" s="1" t="s">
@@ -2118,13 +2131,13 @@
       <c r="I3" s="6" t="s">
         <v>157</v>
       </c>
-      <c r="J3" s="21">
+      <c r="J3" s="2">
         <f t="shared" si="0"/>
         <v>8.5</v>
       </c>
-      <c r="K3" s="21">
+      <c r="K3" s="2">
         <f t="shared" si="1"/>
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="L3" s="2">
         <v>9</v>
@@ -2158,7 +2171,7 @@
       <c r="E4" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="F4" s="3">
+      <c r="F4" s="1">
         <v>120</v>
       </c>
       <c r="G4" s="1" t="s">
@@ -2170,13 +2183,13 @@
       <c r="I4" s="6" t="s">
         <v>160</v>
       </c>
-      <c r="J4" s="21">
+      <c r="J4" s="2">
         <f t="shared" si="0"/>
         <v>8.375</v>
       </c>
-      <c r="K4" s="21">
+      <c r="K4" s="2">
         <f t="shared" si="1"/>
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="L4" s="2">
         <v>8.5</v>
@@ -2210,7 +2223,7 @@
       <c r="E5" s="1" t="s">
         <v>165</v>
       </c>
-      <c r="F5" s="3">
+      <c r="F5" s="1">
         <v>60</v>
       </c>
       <c r="G5" s="1" t="s">
@@ -2222,11 +2235,11 @@
       <c r="I5" s="6" t="s">
         <v>166</v>
       </c>
-      <c r="J5" s="21">
+      <c r="J5" s="2">
         <f t="shared" si="0"/>
         <v>9.25</v>
       </c>
-      <c r="K5" s="21">
+      <c r="K5" s="2">
         <f t="shared" si="1"/>
         <v>3</v>
       </c>
@@ -2262,7 +2275,7 @@
       <c r="E6" s="1" t="s">
         <v>171</v>
       </c>
-      <c r="F6" s="3">
+      <c r="F6" s="1">
         <v>90</v>
       </c>
       <c r="G6" s="1" t="s">
@@ -2274,13 +2287,13 @@
       <c r="I6" s="9" t="s">
         <v>172</v>
       </c>
-      <c r="J6" s="21">
+      <c r="J6" s="2">
         <f t="shared" si="0"/>
         <v>8.75</v>
       </c>
-      <c r="K6" s="21">
+      <c r="K6" s="2">
         <f t="shared" si="1"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L6" s="2">
         <v>9</v>
@@ -2314,7 +2327,7 @@
       <c r="E7" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="F7" s="3">
+      <c r="F7" s="1">
         <v>90</v>
       </c>
       <c r="G7" s="1" t="s">
@@ -2326,13 +2339,13 @@
       <c r="I7" s="9" t="s">
         <v>176</v>
       </c>
-      <c r="J7" s="21">
+      <c r="J7" s="2">
         <f t="shared" si="0"/>
         <v>8.25</v>
       </c>
-      <c r="K7" s="21">
+      <c r="K7" s="2">
         <f t="shared" si="1"/>
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="L7" s="2">
         <v>8</v>
@@ -2366,7 +2379,7 @@
       <c r="E8" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="F8" s="3">
+      <c r="F8" s="1">
         <v>90</v>
       </c>
       <c r="G8" s="1" t="s">
@@ -2378,13 +2391,13 @@
       <c r="I8" s="9" t="s">
         <v>181</v>
       </c>
-      <c r="J8" s="21">
+      <c r="J8" s="2">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
-      <c r="K8" s="21">
+      <c r="K8" s="2">
         <f t="shared" si="1"/>
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="L8" s="2">
         <v>8</v>
@@ -2418,7 +2431,7 @@
       <c r="E9" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="F9" s="3">
+      <c r="F9" s="1">
         <v>80</v>
       </c>
       <c r="G9" s="1" t="s">
@@ -2430,13 +2443,13 @@
       <c r="I9" s="9" t="s">
         <v>185</v>
       </c>
-      <c r="J9" s="21">
+      <c r="J9" s="2">
         <f t="shared" si="0"/>
         <v>8.5</v>
       </c>
-      <c r="K9" s="21">
+      <c r="K9" s="2">
         <f t="shared" si="1"/>
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="L9" s="2">
         <v>8</v>
@@ -2470,7 +2483,7 @@
       <c r="E10" s="1" t="s">
         <v>190</v>
       </c>
-      <c r="F10" s="3">
+      <c r="F10" s="1">
         <v>70</v>
       </c>
       <c r="G10" s="1" t="s">
@@ -2482,13 +2495,13 @@
       <c r="I10" s="9" t="s">
         <v>191</v>
       </c>
-      <c r="J10" s="21">
+      <c r="J10" s="2">
         <f t="shared" si="0"/>
         <v>7.5</v>
       </c>
-      <c r="K10" s="21">
+      <c r="K10" s="2">
         <f t="shared" si="1"/>
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="L10" s="2">
         <v>7</v>
@@ -2519,7 +2532,7 @@
       <c r="E11" s="1" t="s">
         <v>195</v>
       </c>
-      <c r="F11" s="3">
+      <c r="F11" s="1">
         <v>60</v>
       </c>
       <c r="G11" s="1" t="s">
@@ -2531,13 +2544,13 @@
       <c r="I11" s="9" t="s">
         <v>196</v>
       </c>
-      <c r="J11" s="21">
+      <c r="J11" s="2">
         <f t="shared" si="0"/>
         <v>6.75</v>
       </c>
-      <c r="K11" s="21">
+      <c r="K11" s="2">
         <f t="shared" si="1"/>
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="L11" s="2">
         <v>7</v>
@@ -2555,26 +2568,26 @@
         <v>197</v>
       </c>
     </row>
-    <row r="12" spans="1:16" ht="13.2">
-      <c r="A12" s="2" t="s">
+    <row r="12" spans="1:16" ht="15">
+      <c r="A12" s="1" t="s">
         <v>198</v>
       </c>
-      <c r="B12" s="2" t="s">
+      <c r="B12" s="1" t="s">
         <v>199</v>
       </c>
-      <c r="C12" s="2" t="s">
+      <c r="C12" s="1" t="s">
         <v>200</v>
       </c>
-      <c r="D12" s="2" t="s">
+      <c r="D12" s="1" t="s">
         <v>201</v>
       </c>
-      <c r="E12" s="2" t="s">
+      <c r="E12" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="F12" s="2">
+      <c r="F12" s="1">
         <v>75</v>
       </c>
-      <c r="G12" s="2" t="s">
+      <c r="G12" s="1" t="s">
         <v>202</v>
       </c>
       <c r="H12" s="17">
@@ -2583,13 +2596,13 @@
       <c r="I12" s="14" t="s">
         <v>203</v>
       </c>
-      <c r="J12" s="21">
+      <c r="J12" s="2">
         <f t="shared" si="0"/>
         <v>8.125</v>
       </c>
-      <c r="K12" s="21">
+      <c r="K12" s="2">
         <f t="shared" si="1"/>
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="L12" s="2">
         <v>8</v>
@@ -2607,26 +2620,26 @@
         <v>204</v>
       </c>
     </row>
-    <row r="13" spans="1:16" ht="13.2">
-      <c r="A13" s="2" t="s">
+    <row r="13" spans="1:16" ht="15">
+      <c r="A13" s="1" t="s">
         <v>205</v>
       </c>
-      <c r="B13" s="2" t="s">
+      <c r="B13" s="1" t="s">
         <v>199</v>
       </c>
-      <c r="C13" s="2" t="s">
+      <c r="C13" s="1" t="s">
         <v>200</v>
       </c>
-      <c r="D13" s="2" t="s">
+      <c r="D13" s="1" t="s">
         <v>201</v>
       </c>
-      <c r="E13" s="2" t="s">
+      <c r="E13" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="F13" s="2">
+      <c r="F13" s="1">
         <v>90</v>
       </c>
-      <c r="G13" s="2" t="s">
+      <c r="G13" s="1" t="s">
         <v>202</v>
       </c>
       <c r="H13" s="17">
@@ -2635,13 +2648,13 @@
       <c r="I13" s="14" t="s">
         <v>206</v>
       </c>
-      <c r="J13" s="21">
+      <c r="J13" s="2">
         <f t="shared" si="0"/>
         <v>7.375</v>
       </c>
-      <c r="K13" s="21">
+      <c r="K13" s="2">
         <f t="shared" si="1"/>
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="L13" s="2">
         <v>7</v>
@@ -2675,7 +2688,7 @@
       <c r="E14" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="F14" s="3">
+      <c r="F14" s="1">
         <v>360</v>
       </c>
       <c r="G14" s="1" t="s">
@@ -2684,13 +2697,14 @@
       <c r="H14" s="3">
         <v>10</v>
       </c>
-      <c r="I14" s="22" t="s">
+      <c r="I14" s="21" t="s">
         <v>211</v>
       </c>
-      <c r="J14">
+      <c r="J14" s="2">
+        <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="K14" s="21">
+      <c r="K14" s="2">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
@@ -2706,7 +2720,7 @@
       <c r="O14" s="2">
         <v>10</v>
       </c>
-      <c r="P14" s="23" t="s">
+      <c r="P14" s="22" t="s">
         <v>212</v>
       </c>
     </row>
@@ -2726,7 +2740,7 @@
       <c r="E15" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="F15" s="3">
+      <c r="F15" s="1">
         <v>80</v>
       </c>
       <c r="G15" s="1" t="s">
@@ -2738,12 +2752,13 @@
       <c r="I15" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="J15" s="1">
-        <v>6</v>
-      </c>
-      <c r="K15" s="21">
+      <c r="J15" s="2">
+        <f t="shared" si="0"/>
+        <v>8.75</v>
+      </c>
+      <c r="K15" s="2">
         <f t="shared" si="1"/>
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="L15" s="2">
         <v>9.5</v>
@@ -2757,8 +2772,60 @@
       <c r="O15" s="2">
         <v>8</v>
       </c>
-      <c r="P15" s="23" t="s">
+      <c r="P15" s="22" t="s">
         <v>214</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" ht="15.75" customHeight="1">
+      <c r="A16" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="F16" s="1">
+        <v>120</v>
+      </c>
+      <c r="G16" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H16" s="1" t="s">
+        <v>218</v>
+      </c>
+      <c r="I16" s="23" t="s">
+        <v>219</v>
+      </c>
+      <c r="J16" s="2">
+        <f t="shared" si="0"/>
+        <v>9.25</v>
+      </c>
+      <c r="K16" s="2">
+        <f t="shared" si="1"/>
+        <v>3</v>
+      </c>
+      <c r="L16" s="2">
+        <v>9</v>
+      </c>
+      <c r="M16" s="2">
+        <v>9</v>
+      </c>
+      <c r="N16" s="2">
+        <v>9</v>
+      </c>
+      <c r="O16" s="2">
+        <v>10</v>
+      </c>
+      <c r="P16" s="22" t="s">
+        <v>215</v>
       </c>
     </row>
   </sheetData>
@@ -2777,6 +2844,7 @@
     <hyperlink ref="I13" r:id="rId12" xr:uid="{00000000-0004-0000-0100-00000B000000}"/>
     <hyperlink ref="I14" r:id="rId13" xr:uid="{E4DAB110-E83E-4DEC-A2CC-8650550F459C}"/>
     <hyperlink ref="I15" r:id="rId14" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
+    <hyperlink ref="I16" r:id="rId15" xr:uid="{97E800A5-A381-4541-8F47-9D0EB0072863}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
